--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260502_203119.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260502_203119.xlsx
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
